--- a/evidence/independent_sample_2.xlsx
+++ b/evidence/independent_sample_2.xlsx
@@ -78,7 +78,7 @@
     <t>snapshot_id</t>
   </si>
   <si>
-    <t>8145eba6e6d2c8896f8e87dfc19ffb1f</t>
+    <t>bfdb5bb40424dc47237c7c6aa36e6cd7</t>
   </si>
   <si>
     <t>integration_id</t>
@@ -120,13 +120,13 @@
     <t>source_snapshot_ref</t>
   </si>
   <si>
-    <t>e396a7637215b6337223d2e1c5588949</t>
+    <t>a10fd530d9fa99be237c2d15c42d6993</t>
   </si>
   <si>
     <t>expires_at</t>
   </si>
   <si>
-    <t>2026-10-26T14:13:18+08:00</t>
+    <t>2026-10-26T14:26:19+08:00</t>
   </si>
   <si>
     <t>precision</t>
